--- a/data/product_scoring/product_list_iter_1_test_22_06_2026.xlsx
+++ b/data/product_scoring/product_list_iter_1_test_22_06_2026.xlsx
@@ -456,7 +456,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -486,10 +486,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1414,7 +1410,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
@@ -1588,7 +1584,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
@@ -1752,7 +1748,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
@@ -1925,7 +1921,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
@@ -2097,7 +2093,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
@@ -2259,7 +2255,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
@@ -2420,7 +2416,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
@@ -2506,7 +2502,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="12" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
         <v>11</v>
       </c>
@@ -2663,7 +2659,7 @@
       <c r="W13" s="3" t="n">
         <v>0.0779</v>
       </c>
-      <c r="X13" s="9" t="n">
+      <c r="X13" s="8" t="n">
         <f aca="false">AVERAGE(4.8,4.7,4.8,4.8,4.7,4.9,4.8,4.9,4.9,4.9,4.9,4.8,4.8,4.8)</f>
         <v>4.82142857142857</v>
       </c>
@@ -2783,7 +2779,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
@@ -2972,7 +2968,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
@@ -3152,7 +3148,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
@@ -3329,7 +3325,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
@@ -3491,7 +3487,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
